--- a/reports/arsenal/军火榜_2026-09-09.xlsx
+++ b/reports/arsenal/军火榜_2026-09-09.xlsx
@@ -633,19 +633,19 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>multica-ai/andrej-karpathy-skills</t>
+          <t>ruvnet/RuView</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>211865</v>
+        <v>92914</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>6591.3</v>
+        <v>1417</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>改进 Claude Code 行为的 CLAUDE.md 文件
-【原文】A single CLAUDE.md file to improve Claude Code behavior, derived from Andrej Karpathy's observations on LLM coding pitfalls.</t>
+          <t>将WiFi信号转换为实时空间智能、生命体征监测和存在检测
+【原文】π RuView turns commodity WiFi signals into real-time spatial intelligence, vital sign monitoring, and presence detection — all without a single pixel of video.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/multica-ai/andrej-karpathy-skills</t>
+          <t>https://github.com/ruvnet/RuView</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,14 +679,18 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>941.62</v>
+        <v>202.43</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -697,22 +701,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>awesome, claude, densepose, esp32, firmware, home-assistant, home-automation, iot, monitoring, networking, npm, pose-estimation</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>225</v>
+        <v>459</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
@@ -721,42 +729,41 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name,description stars:&gt;50000</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Player-YN/PawWork_ZhuaZhua</t>
+          <t>tinyhumansai/openhuman</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2277</v>
+        <v>39576</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1328.2</v>
+        <v>1364.7</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Paw Work - Chrome浏览器选择优先的Web代理
-【原文】Paw Work - selection-first web agent for Chrome: select on the live page, describe the outcome, take away an editable office file. BYOK, sandboxed, no server.
-【依据】topics: ai-agent, browser-agent, chrome-extension, llm</t>
+          <t>开源个人AI，支持本地存储和代理编排
+【原文】OpenHuman is an open source personal AI for Mac, Windows and Linux — local-first memory, agent orchestration, and deep research.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>MCP服务/技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -766,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Player-YN/PawWork_ZhuaZhua</t>
+          <t>https://github.com/tinyhumansai/openhuman</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -775,16 +782,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>189.75</v>
+        <v>194.96</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -799,12 +806,12 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, browser-agent, byok, chrome-extension, llm, pptx, tldraw, univer</t>
+          <t>agent-orchestration, ai-agents, ai-assistant, desktop, llm, local-first, mcp, personal-ai, privacy, rust, second-brain, tauri</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -813,7 +820,7 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>12</v>
+        <v>203</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -825,41 +832,42 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>bytedance/deer-flow</t>
+          <t>codecrafters-io/build-your-own-x</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>82135</v>
+        <v>546232</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1173.3</v>
+        <v>1255.7</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>开源长周期 SuperAgent 框架，用于研究和创建
-【原文】An open-source long-horizon SuperAgent harness that researches, codes, and creates. With the help of sandboxes, memories, tools, skill, subagents and message gateway, it handles different levels of tasks that could take minutes to hours.</t>
+          <t>编程技术教程
+【原文】Master programming by recreating your favorite technologies from scratch.
+【依据】programming, tutorial-code, tutorials</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考/可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -869,7 +877,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bytedance/deer-flow</t>
+          <t>https://github.com/codecrafters-io/build-your-own-x</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -878,16 +886,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>167.62</v>
+        <v>179.39</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Markdown</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -902,21 +910,21 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic, agentic-framework, agentic-workflow, ai, ai-agents, deep-research, harness, langchain, langgraph, langmanus, llm</t>
+          <t>awesome-list, free, programming, tutorial-code, tutorial-exercises, tutorials</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>490</v>
+        <v>3045</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -928,36 +936,36 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>skill in:name,description stars:&gt;50000</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>genspark-ai/genoffice</t>
+          <t>truefoundry/trueforge</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6304</v>
+        <v>5349</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1103.2</v>
+        <v>780.1</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供类似 Microsoft Office 的 AI 办公软件替代品。
-【原文】Free, open-source alternative to Microsoft Office with built-in AI agents — Word (.docx), Excel (.xlsx), PowerPoint (.pptx), PDF and Markdown editing for macOS, Windows &amp; Linux.</t>
+          <t>将LLM转换为工作代理的开源代理 harness
+【原文】The open-source agent harness - the runtime layer that turns an LLM into a working agent.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -972,7 +980,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/genspark-ai/genoffice</t>
+          <t>https://github.com/truefoundry/trueforge</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -981,11 +989,11 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>157.6</v>
+        <v>111.44</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1005,12 +1013,12 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic, ai, ai-agent, ai-agents, ai-office, docx, excel, markdown-editor, microsoft-office, office, office-agent</t>
+          <t>agent, agentic-ai, agents, harness, harness-engineering</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1019,53 +1027,54 @@
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Vincentwei1021/video-shotcraft</t>
+          <t>donnemartin/system-design-primer</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>7902</v>
+        <v>369020</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1063.7</v>
+        <v>741.9</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>为 Claude Code &amp; Codex 提供AI视频技能，制作产品视频
-【原文】AI video skill for Claude Code &amp; Codex — cinematic product videos with Remotion: 152 shot recipe cards, 209 motion previews, a production-ready template</t>
+          <t>系统设计学习资源
+【原文】Learn how to design large-scale systems. Prep for the system design interview.  Includes Anki flashcards.
+【依据】design, system, web-application</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1075,7 +1084,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Vincentwei1021/video-shotcraft</t>
+          <t>https://github.com/donnemartin/system-design-primer</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1084,16 +1093,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>151.96</v>
+        <v>105.98</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1108,21 +1117,21 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, ai-video, claude-code, claude-code-skills, claude-skills, codex, motion-design, motion-graphics, product-video, promo-video, remotion</t>
+          <t>design, design-patterns, design-system, development, interview, interview-practice, interview-questions, programming, python, system, web, web-application</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>52</v>
+        <v>3482</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1134,40 +1143,42 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>yang0/handraw-style</t>
+          <t>996icu/996.ICU</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>604</v>
+        <v>276933</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1057</v>
+        <v>711.6</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供手绘风格编号画廊与双语提示词 Skill</t>
+          <t>统计贡献者仓库
+【原文】Repo for counting stars and contributing. Press F to pay respect to glorious developers.
+【依据】-</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1177,7 +1188,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yang0/handraw-style</t>
+          <t>https://github.com/996icu/996.ICU</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1186,18 +1197,14 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>151</v>
+        <v>101.66</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1211,47 +1218,48 @@
       <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>4</v>
+        <v>2724</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MDX-Tom/gpt-instruct</t>
+          <t>jwasham/coding-interview-university</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7940</v>
+        <v>360645</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>926.3</v>
+        <v>673.8</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供针对 gpt 系列的 Codex 破甲提示词与测试包
-【原文】A Codex jailbreak prompt and test pack for gpt. 针对 gpt 系列的 Codex 破甲提示词与测试包。</t>
+          <t>软件工程师学习计划
+【原文】A complete computer science study plan to become a software engineer.
+【依据】algorithm, coding-interview, software-engineering</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1261,12 +1269,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1276,7 +1284,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MDX-Tom/gpt-instruct</t>
+          <t>https://github.com/jwasham/coding-interview-university</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1285,18 +1293,14 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>132.33</v>
+        <v>96.25</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>CC-BY-SA-4.0</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1307,50 +1311,55 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>algorithm, algorithms, coding-interview, coding-interviews, computer-science, data-structures, interview, interview-prep, interview-preparation, programming-interviews, software-engineering, study-plan</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>60</v>
+        <v>3747</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>EvoLinkAI/awesome-gpt-image-2-API-and-Prompts</t>
+          <t>trimstray/the-book-of-secret-knowledge</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>17139</v>
+        <v>242884</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>833.1</v>
+        <v>566.7</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供 GPT-Image-2 API 和提示词
-【原文】GPT-Image-2 API and Prompts</t>
+          <t>收集技术资源列表
+【原文】A collection of inspiring lists, manuals, cheatsheets, blogs, hacks, one-liners, cli/web tools and more.
+【依据】awesome, cheatsheets, devops</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1360,7 +1369,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1375,7 +1384,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/EvoLinkAI/awesome-gpt-image-2-API-and-Prompts</t>
+          <t>https://github.com/trimstray/the-book-of-secret-knowledge</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1384,18 +1393,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>119.02</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1408,21 +1413,21 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>ai-art, api, awesome-list, awesome-lists, chatgpt, creative-tools, generative-ai, gpt-image-2, gpt-image-2-api, gpt-image-2-prompts, gptimage2, image-generation</t>
+          <t>awesome, awesome-list, bsd, cheatsheets, devops, guidelines, hacking, hacks, howtos, linux, lists, manuals</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>144</v>
+        <v>3000</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1434,26 +1439,27 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>hacksider/Deep-Live-Cam</t>
+          <t>massgravel/Microsoft-Activation-Scripts</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>96578</v>
+        <v>189923</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>625.4</v>
+        <v>546.6</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>实现实时面部交换和一键视频深度伪造
-【原文】real time face swap and one-click video deepfake with only a single image</t>
+          <t>Windows 和 Office 激活脚本
+【原文】Open-source Windows and Office activator featuring HWID, Ohook, TSforge, and Online KMS activation methods, along with advanced troubleshooting.
+【依据】activator, hwid, kms</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1463,7 +1469,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1478,7 +1484,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hacksider/Deep-Live-Cam</t>
+          <t>https://github.com/massgravel/Microsoft-Activation-Scripts</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1487,16 +1493,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>89.34</v>
+        <v>78.09</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Batchfile</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1511,21 +1517,21 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-deep-fake, ai-face, ai-webcam, artificial-intelligence, deep-fake, deepfake, deepfake-webcam, faceswap, fake-webcam, gan, real-time-deepfake</t>
+          <t>activator, hwid, kms, kms38, massgrave, massgravel, microsoft, microsoft365, office, office365, ohook, powershell</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2020-01-12</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1081</v>
+        <v>2432</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1537,26 +1543,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>unslothai/unsloth</t>
+          <t>charmbracelet/crush</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>75948</v>
+        <v>27978</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>523.8</v>
+        <v>411.5</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供本地 UI 运行和训练 LLMs 和扩散模型。
-【原文】Local UI to run and train LLMs and diffusion models. Supports GGUF, MLX, Qwen3.8, DeepSeek-V4, MiniMax-H3, Gemma 4, FLUX and more.</t>
+          <t>用于所有AI代理的华丽编码工具
+【原文】Glamourous agentic coding for all 💘</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1566,12 +1572,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1581,7 +1587,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/unslothai/unsloth</t>
+          <t>https://github.com/charmbracelet/crush</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1590,16 +1596,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>74.83</v>
+        <v>58.78</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1614,12 +1620,12 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, chatgpt, deepseek, fine-tuning, gemma, image-generation, llama, llm, llms, openai, python</t>
+          <t>agentic-ai, ai, llms, ravishing</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1628,7 +1634,7 @@
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>1015</v>
+        <v>476</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1640,40 +1646,41 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>yilujian/easy-writing</t>
+          <t>ZJU-REAL/Easel</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>506</v>
+        <v>700</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>393.5</v>
+        <v>408.3</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>纯本地、开源的 AI 网文写作桌面软件</t>
+          <t>社交媒体AI智能体，用于内容创作和发布
+【原文】An open-source AI agent for social media — discover trends, create content, publish everywhere, and learn what works across Xiaohongshu, Douyin, Zhihu, Bilibili, and more.🎨一个开源的 AI 社交媒体智能体——发现热点趋势、创作内容、一键发布至各大平台，并学习分析哪些内容真正有效，覆盖小红书、抖音、知乎、哔哩哔哩等平台。</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>MCP服务/技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1683,7 +1690,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yilujian/easy-writing</t>
+          <t>https://github.com/ZJU-REAL/Easel</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1692,16 +1699,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>56.22</v>
+        <v>58.33</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1716,21 +1723,21 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>ai-writing, ai-writing-assistant, byok, creative-writing, desktop-app, local-first, novel-writing, openai-compatible, tauri, vue3, web-novel, writing-tools</t>
+          <t>agent, agent-skill, content-automation, content-creation, content-generation, mcp, openclaw, social-media, social-media-management</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1742,36 +1749,36 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>nexu-io/html-video</t>
+          <t>run-llama/liteparse</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4559</v>
+        <v>12278</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>303.9</v>
+        <v>405.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>将 HTML、CSS 和数据转换为 MP4 视频的编程工具
-【原文】Programmatic video for coding agents — HTML to video on your laptop. Turn HTML, CSS &amp; data into real MP4s with pluggable render engines, 21 templates, AI soundtrack. Apache-2.0, no per-render fees. An official project by the Open Design team.</t>
+          <t>快速、有用的开源文档解析器
+【原文】A fast, helpful, and open-source document parser</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1786,7 +1793,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/nexu-io/html-video</t>
+          <t>https://github.com/run-llama/liteparse</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1795,7 +1802,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>43.42</v>
+        <v>57.92</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1804,7 +1811,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1819,21 +1826,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, apache-2, coding-agent, css, ffmpeg, html, html-to-video, hyperframes, mp4, open-design, open-source, programmatic-video</t>
+          <t>document-ocr, document-processing, ocr, ocr-recognition, pdf, pdf-parser, text-extraction</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1845,26 +1852,27 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>florinpop17/app-ideas</t>
+          <t>op7418/guizang-yingzao-skill</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>97431</v>
+        <v>396</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>247.7</v>
+        <v>396</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>收集应用想法以提升编码技能
-【原文】A Collection of application ideas which can be used to improve your coding skills.</t>
+          <t>将中国古建筑和文化照片转换为艺术海报
+【原文】🏯 Claude Code / Codex skill — transform Chinese architecture, cultural places &amp; travel photos into art-directed editorial posters with GPT Image. 中国古建筑与在地文化照片 → 艺术指导海报
+【依据】agent-skill, ai-agent, image-generation</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1874,12 +1882,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1889,7 +1897,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/florinpop17/app-ideas</t>
+          <t>https://github.com/op7418/guizang-yingzao-skill</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1898,14 +1906,18 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>35.39</v>
+        <v>56.57</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1918,21 +1930,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>applications, coding, codingchallenges, css, hacktoberfest, html, ideas, javascript, practice</t>
+          <t>agent-skill, ai-agent, anthropic, chinese-architecture, chinese-culture, claude-code, claude-skill, codex, cultural-heritage, editorial-design, gpt-image, image-generation</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>2753</v>
+        <v>7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1944,40 +1956,42 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>skill in:name,description stars:&gt;50000</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>LancelotRar/best-cf-ips</t>
+          <t>HKUDS/LightRAG</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1159</v>
+        <v>39517</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>165.5</v>
+        <v>391.2</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>提供自动更新的 Cloudflare 优选 IP API</t>
+          <t>提供简单快速的检索增强生成模型
+【原文】[EMNLP2025] LightRAG: Simple and Fast Retrieval-Augmented Generation
+【依据】topics: retrieval-augmented-generation</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1987,7 +2001,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LancelotRar/best-cf-ips</t>
+          <t>https://github.com/HKUDS/LightRAG</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1996,14 +2010,18 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>23.65</v>
+        <v>55.89</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2014,10 +2032,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>docling, genai, gpt, graphrag, knowledge-graph, large-language-models, llm, mineru, rag, ragas, retrieval-augmented-generation</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2026,48 +2048,49 @@
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>49</v>
+        <v>707</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HKUDS/ViMax</t>
+          <t>ossu/computer-science</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>12313</v>
+        <v>208873</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>163.2</v>
+        <v>324.1</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>全功能视频生成系统，包括导演、编剧、制片人和视频生成
-【原文】"ViMax: Agentic Video Generation (Director, Screenwriter, Producer, and Video Generator All-in-One)"</t>
+          <t>计算机科学学习路径
+【原文】🎓 Path to a free self-taught education in Computer Science!
+【依据】computer-science, courses, curriculum</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2082,7 +2105,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HKUDS/ViMax</t>
+          <t>https://github.com/ossu/computer-science</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2091,7 +2114,7 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>23.32</v>
+        <v>46.3</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2100,7 +2123,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2115,21 +2138,21 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>agentic-aigc, video-generation</t>
+          <t>awesome-list, computer-science, courses, curriculum</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2014-05-04</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>528</v>
+        <v>4511</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2141,37 +2164,37 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Anil-matcha/Open-Generative-AI</t>
+          <t>vuejs/vue</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>28193</v>
+        <v>212027</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>161.9</v>
+        <v>309.8</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>开源AI视频平台替代品，提供图像和视频生成
-【原文】Unrestricted Open-source alternative to AI video platforms — Free AI image &amp; video generation studio with 600+ models (Flux, Midjourney, Kling, Sora, Veo). No content filters. Self-hosted, MIT licensed.
-【依据】topics: ai-art-generator, ai-image-generation, ai-video-generation, creative-tools, image-to-video</t>
+          <t>Vue.js 框架仓库
+【原文】This is the repo for Vue 2. For Vue 3, go to https://github.com/vuejs/core
+【依据】framework, frontend, javascript</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2186,7 +2209,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Anil-matcha/Open-Generative-AI</t>
+          <t>https://github.com/vuejs/vue</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2195,7 +2218,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>23.13</v>
+        <v>44.26</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2227,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2219,24 +2242,24 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>ai-art-generator, ai-image-generation, ai-video-generation, creative-tools, fal-ai-alternative, generative-ai, image-to-video, invideo-alternative, javascript, kling-ai, lipsync, midjourney-alternative</t>
+          <t>framework, frontend, javascript, vue</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2013-07-29</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>1219</v>
+        <v>4790</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
@@ -2245,36 +2268,36 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>3b1b/manim</t>
+          <t>google/adk-python</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>93637</v>
+        <v>21470</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>156.5</v>
+        <v>285.7</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>用于制作解释性数学视频的动画引擎
-【原文】Animation engine for explanatory math videos</t>
+          <t>构建、评估和部署复杂AI代理的Python工具包
+【原文】An open-source, code-first Python toolkit for building, evaluating, and deploying sophisticated AI agents with flexibility and control.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2289,7 +2312,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/3b1b/manim</t>
+          <t>https://github.com/google/adk-python</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2298,11 +2321,11 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>22.35</v>
+        <v>40.82</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -2322,12 +2345,12 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>3b1b-videos, animation, explanatory-math-videos, python</t>
+          <t>agent, agentic, agentic-ai, agents, agents-sdk, ai, ai-agents, aiagentframework, genai, genai-chatbot, llm, llms</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2015-03-22</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2336,7 +2359,7 @@
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>4189</v>
+        <v>526</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2348,36 +2371,36 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>huggingface/diffusers</t>
+          <t>alvinunreal/oh-my-opencode-slim</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>34475</v>
+        <v>8751</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>154.4</v>
+        <v>258.4</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>提供 PyTorch 中的图像、视频和音频生成模型
-【原文】🤗 Diffusers: State-of-the-art diffusion models for image, video, and audio generation in PyTorch.</t>
+          <t>精调的Opencode多代理套件，混合任何模型
+【原文】Lean, fine tuned Opencode multi agent suite · Mix any models · Auto delegate tasks</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>视频产线/图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2392,7 +2415,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/huggingface/diffusers</t>
+          <t>https://github.com/alvinunreal/oh-my-opencode-slim</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2401,16 +2424,16 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>22.06</v>
+        <v>36.92</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2425,12 +2448,12 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>deep-learning, diffusion, flux, image-generation, image2image, image2video, latent-diffusion-models, pytorch, qwen-image, score-based-generative-modeling, stable-diffusion, stable-diffusion-diffusers</t>
+          <t>agentic-ai, antigravity, cerebras, herdr-plugin, oh-my-opencode, opencode, orchestration</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -2439,10 +2462,10 @@
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>1563</v>
+        <v>237</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
@@ -2451,26 +2474,26 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>khoj-ai/khoj</t>
+          <t>Asabeneh/30-Days-Of-Python</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>37229</v>
+        <v>73264</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>140.8</v>
+        <v>206.3</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供个人 AI 助手，可自托管。
-【原文】Your AI second brain. Self-hostable. Get answers from the web or your docs. Build custom agents, schedule automations, do deep research. Turn any online or local LLM into your personal, autonomous AI (gpt, claude, gemini, llama, qwen, mistral). Get started - free.</t>
+          <t>提供Python编程挑战的指南和视频
+【原文】The 30 Days of Python programming challenge is a step-by-step guide to learn the Python programming language in 30 days. This challenge may take more than 100 days. Follow your own pace. These videos may help too: https://www.youtube.com/channel/UC7PNRuno1rzYPb1xLa4yktw</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2480,12 +2503,12 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2495,7 +2518,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/khoj-ai/khoj</t>
+          <t>https://github.com/Asabeneh/30-Days-Of-Python</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2504,11 +2527,11 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>20.12</v>
+        <v>29.47</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2528,21 +2551,21 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, assistant, chat, chatgpt, emacs, image-generation, llama3, llamacpp, llm, obsidian, obsidian-md</t>
+          <t>30-days-of-python, data, data-science, database, flask, fullstack, github, heroku, matplotlib, ml, mongodb, numpy</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2019-11-19</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1850</v>
+        <v>2486</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2554,26 +2577,26 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Robbyant/lingbot-world</t>
+          <t>ChenShuo2004/cs-board</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>4423</v>
+        <v>541</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>138.2</v>
+        <v>199.3</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>推进开源世界模型的发展
-【原文】Advancing Open-source World Models</t>
+          <t>生成白板动画视频的AI工具
+【原文】将参考声音和中文文案自动生成白板动画视频的本地 AI 工具。</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2598,7 +2621,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Robbyant/lingbot-world</t>
+          <t>https://github.com/ChenShuo2004/cs-board</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2607,11 +2630,11 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>19.75</v>
+        <v>28.47</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2631,67 +2654,68 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>aigc, image-to-video, lingbot-world, video-generation, world-models</t>
+          <t>ai-video, chinese, fastapi, index-tts, react, tts, whiteboard-animation</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>224</v>
+        <v>19</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Tencent-Hunyuan/HunyuanVideo</t>
+          <t>topoteretes/cognee</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>12508</v>
+        <v>30607</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>134.7</v>
+        <v>191.3</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>大型视频生成模型系统框架
-【原文】HunyuanVideo: A Systematic Framework For Large Video Generation Model</t>
+          <t>为AI代理提供持久长期记忆的知识图谱引擎
+【原文】Cognee is the open-source AI memory platform for agents. Give your AI agents persistent long-term memory across sessions with a self-hosted knowledge graph engine.
+【依据】topics: cognitive-architecture, cognitive-memory</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -2701,7 +2725,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Tencent-Hunyuan/HunyuanVideo</t>
+          <t>https://github.com/topoteretes/cognee</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2710,11 +2734,11 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>19.24</v>
+        <v>27.33</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2734,21 +2758,21 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>diffusion-models, diffusion-transformer, video-generation</t>
+          <t>agent-memory, agent-skills, ai, ai-agents, ai-memory, cognitive-architecture, cognitive-memory, context-engineering, contributions-welcome, good-first-issue, good-first-pr, graph-database</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>650</v>
+        <v>1120</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
@@ -2760,36 +2784,36 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>invoke-ai/InvokeAI</t>
+          <t>microsoft/agent-framework</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>28173</v>
+        <v>13436</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>132.9</v>
+        <v>188.5</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>提供 Stable Diffusion 模型的创意引擎
-【原文】Invoke is a leading creative engine for Stable Diffusion models, empowering professionals, artists, and enthusiasts to generate and create visual media using the latest AI-driven technologies. The solution offers an industry leading WebUI, and serves as the foundation for multiple commercial products.</t>
+          <t>构建、编排和部署AI代理和多代理工作流的框架
+【原文】A framework for building, orchestrating and deploying AI agents and multi-agent workflows with support for Python and .NET.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库/技能包</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2804,7 +2828,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/invoke-ai/InvokeAI</t>
+          <t>https://github.com/microsoft/agent-framework</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2813,11 +2837,11 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>18.98</v>
+        <v>26.93</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2837,21 +2861,21 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>ai-art, artificial-intelligence, generative-art, image-generation, img2img, inpainting, latent-diffusion, linux, macos, outpainting, stable-diffusion, txt2img</t>
+          <t>agent-framework, agentic-ai, agents, ai, dotnet, multi-agent, orchestration, python, sdk, workflows</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>1484</v>
+        <v>499</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
@@ -2863,41 +2887,41 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>oritera/Cairn</t>
+          <t>remotion-dev/remotion</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2709</v>
+        <v>58732</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>132.6</v>
+        <v>181.2</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 辅助的渗透测试工具。
-【原文】A AI general-purpose state-space search engine, validated first on autonomous penetration testing.</t>
+          <t>使用React编程方式制作视频
+【原文】🎥      Make videos programmatically with React</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -2907,7 +2931,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/oritera/Cairn</t>
+          <t>https://github.com/remotion-dev/remotion</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2916,16 +2940,16 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>18.94</v>
+        <v>25.88</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2940,53 +2964,52 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agent, ai-cybersecurity, ai-hacker, ai-hacking, blackbox-testing, ctf, ctf-tools, llm, penetration-testing, pentesting, red-teaming</t>
+          <t>javascript, react, video</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>143</v>
+        <v>2269</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>ciembor/agent-rules-books</t>
+          <t>Developer-Y/cs-video-courses</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2732</v>
+        <v>83456</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>131</v>
+        <v>161.8</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>AI编码代理的规则/技能
-【原文】AGENTS.md rules / skills for AI coding agents: Codex, Cursor &amp; Claude Code. Inspired by Clean Code, Refactoring, DDD, Clean Architecture and DDIA programming books.
-【依据】topics: agent-rules, agent-skills, claude-code, claude-code-skills</t>
+          <t>提供计算机科学课程视频讲座列表
+【原文】List of Computer Science courses with video lectures.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2996,12 +3019,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -3011,7 +3034,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ciembor/agent-rules-books</t>
+          <t>https://github.com/Developer-Y/cs-video-courses</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3020,11 +3043,11 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>18.71</v>
+        <v>23.12</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr"/>
@@ -3040,62 +3063,62 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>agent-rules, agent-skills, agent-skills-manager, agents-md, agents-rules, agents-skills, agentsmd, ai-agent, ai-skills, claude-code, claude-code-skills, code-quality</t>
+          <t>algorithms, bioinformatics, computational-biology, computational-physics, computer-architecture, computer-science, computer-vision, database-systems, databases, deep-learning, embedded-systems, machine-learning</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2016-10-21</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>146</v>
+        <v>3610</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>vllm-project/vllm-omni</t>
+          <t>OpenPipe/ART</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>6739</v>
+        <v>10707</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>129.9</v>
+        <v>136.8</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>高效模型推理框架，支持多种模态模型
-【原文】A framework for efficient model inference with omni-modality models</t>
+          <t>训练多步骤代理用于现实任务，支持多种LLM
+【原文】Agent Reinforcement Trainer: train multi-step agents for real-world tasks using GRPO. Give your agents on-the-job training. Reinforcement learning for Qwen3.6, GPT-OSS, Llama, and more!</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3110,7 +3133,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vllm-project/vllm-omni</t>
+          <t>https://github.com/OpenPipe/ART</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3119,7 +3142,7 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>18.56</v>
+        <v>19.54</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3143,12 +3166,12 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>audio-generation, diffusion, image-generation, inference, model-serving, multimodal, pytorch, transformer, video-generation, world-model</t>
+          <t>agent, agentic-ai, grpo, llms, lora, qwen, qwen3, reinforcement-learning, rl</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -3157,10 +3180,10 @@
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>363</v>
+        <v>548</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
@@ -3169,27 +3192,26 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>FailproofAI/failproofai</t>
+          <t>Asabeneh/30-Days-Of-JavaScript</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2526</v>
+        <v>46776</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>113.3</v>
+        <v>133.6</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>AI代理可观察性和执行策略
-【原文】Observability and enforcement for AI agent harnesses. Capture every run and runtime reliability with policy enforcement.  40 built-in policies, a local dashboard, no account required with a generous free cloud plan
-【依据】topics: agent-failure, agent-harness, agent-observability, agent-reliability</t>
+          <t>提供JavaScript编程挑战的指南和视频
+【原文】30 days of JavaScript programming challenge is a step-by-step guide to learn JavaScript programming language in 30 days. This challenge may take more than 100 days,  please just follow your own pace. These videos may help too: https://www.youtube.com/channel/UC7PNRuno1rzYPb1xLa4yktw</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3199,12 +3221,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -3214,7 +3236,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FailproofAI/failproofai</t>
+          <t>https://github.com/Asabeneh/30-Days-Of-JavaScript</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3223,16 +3245,16 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>16.19</v>
+        <v>19.08</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>MDX</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3247,52 +3269,53 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>agent-failure, agent-harness, agent-observability, agent-reliability, agent-tracing, ai-agent, claude-code, codex, enforcement, evals, guardrails, hermes</t>
+          <t>30daysofjavascript, angular, challenge, css, d3, d3js, html, javascript, javascript-for-everyone, js, json, node</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2019-12-23</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>156</v>
+        <v>2452</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>peter123023/awesome-free-llm-api</t>
+          <t>agentpit-io/hunter-community</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>110</v>
+        <v>497</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>96.2</v>
+        <v>116</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>导航免费大模型 API
-【原文】免费大模型 API 导航 · 只收录能通过 API Key 和 endpoint 调用的永久免费 / 限时免费接口｜A curated list of free LLM APIs — permanently free tiers and limited-time free models, all callable via API key and endpoint. Channel-first, with a model index for DeepSeek, GLM, Qwen and more</t>
+          <t>私人金融AI团队，提供AI智能体和AI量化服务
+【原文】Hunter Community Edition · 私人金融 AI 团队 · AI 智能体 + AI 量化 · 开源自托管 · powered by opencode + Claude Code + MCP + multi-agent · your private financial AI team · open-source self-hosted · 15 min docker start
+【依据】AI智能体 + AI量化 · 开源自托管 · 15 min docker start</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -3317,7 +3340,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/peter123023/awesome-free-llm-api</t>
+          <t>https://github.com/agentpit-io/hunter-community</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3326,14 +3349,18 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>13.75</v>
+        <v>16.57</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3344,19 +3371,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, ai-hedge-fund, ai-quant, anthropic, apache-2, claude-agent-sdk, claude-code, codex, docker-compose, financial-ai, fintech, llm-agent</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
@@ -3368,27 +3399,26 @@
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NVlabs/Sana</t>
+          <t>yifanfeng97/Hyper-Extract</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>9018</v>
+        <v>3925</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>90.40000000000001</v>
+        <v>112.1</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>基于线性扩散变换器的图像合成系统
-【原文】SANA: Efficient High-Resolution Image Synthesis with Linear Diffusion Transformer
-【依据】topics: diffusion, dit, linear-transformer, pytorch, text-to-image-generation</t>
+          <t>将文本转换为结构化知识的工具
+【原文】Hypergraph is more powerful. Transform unstructured text into structured knowledge with LLMs. Graphs, hypergraphs, and spatio-temporal extractions — with one command.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3398,12 +3428,12 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -3413,7 +3443,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NVlabs/Sana</t>
+          <t>https://github.com/yifanfeng97/Hyper-Extract</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3422,11 +3452,11 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>12.92</v>
+        <v>16.02</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3446,12 +3476,12 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>diffusion, dit, linear-transformer, nvfp4, pytorch, reinforcement-learning, sana, streaming-video, system-algorithm-deisgn, text-to-image-generation, text-to-video, transformers</t>
+          <t>ai, ai-agents, cli, hypergraph, information-extraction, knowledge, knowledge-graph, llm, python, rag</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
@@ -3460,10 +3490,10 @@
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>698</v>
+        <v>245</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
@@ -3472,36 +3502,36 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>GVCLab/PersonaLive</t>
+          <t>thu-ml/TurboDiffusion</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>3690</v>
+        <v>3639</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>89.7</v>
+        <v>92</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>生成直播中的表情丰富的肖像图像动画
-【原文】[CVPR 2026] PersonaLive! : Expressive Portrait Image Animation for Live Streaming</t>
+          <t>加速视频扩散模型
+【原文】TurboDiffusion: 100–200× Acceleration for Video Diffusion Models</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3516,7 +3546,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/GVCLab/PersonaLive</t>
+          <t>https://github.com/thu-ml/TurboDiffusion</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -3525,7 +3555,7 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>12.81</v>
+        <v>13.14</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -3549,21 +3579,21 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>cvpr, cvpr2026, talking-head, video-generation</t>
+          <t>ai-infra, consistency-model, diffusion-models, distillation, inference-acceleration, mlsystem, rcm, sageattention, sparse-linear-attention, video-generation</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S31" s="3" t="n">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>1</v>
@@ -3582,34 +3612,34 @@
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>jujumilk3/leaked-system-prompts</t>
+          <t>iina/iina</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>14924</v>
+        <v>46280</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>86.2</v>
+        <v>91.2</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>收集泄露的系统提示词
-【原文】Collection of leaked system prompts</t>
+          <t>为macOS提供现代视频播放器
+【原文】The modern video player for macOS.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -3619,7 +3649,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jujumilk3/leaked-system-prompts</t>
+          <t>https://github.com/iina/iina</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3628,14 +3658,18 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>12.31</v>
+        <v>13.03</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr"/>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3648,21 +3682,21 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>ai, document, llm, prompt</t>
+          <t>hacktoberfest, macos, mpv, swift, video, video-player</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2016-12-19</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1212</v>
+        <v>3551</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>1</v>
@@ -3674,41 +3708,42 @@
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>PKU-YuanGroup/Helios</t>
+          <t>TriliumNext/Trilium</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2143</v>
+        <v>37775</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>78.5</v>
+        <v>77.8</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>提供实时长视频生成模型。
-【原文】Helios: Real Real-Time Long Video Generation Model</t>
+          <t>构建个人知识库
+【原文】Build your personal knowledge base with Trilium Notes
+【依据】knowledge-base, knowledge-graph, knowledge-management</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3718,7 +3753,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PKU-YuanGroup/Helios</t>
+          <t>https://github.com/TriliumNext/Trilium</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3727,16 +3762,16 @@
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>11.22</v>
+        <v>11.12</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3751,21 +3786,21 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>acceleration, diffusion, diffusion-model, diffusion-models, efficient-tuning, high-quality, image-to-video, image2video, interactive, long-context, long-video-generation, real-time</t>
+          <t>electron, electron-app, knowledge-base, knowledge-graph, knowledge-management, knowledge-management-graph, local-first, note-managment, note-taker, note-taking, notebook, notes</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2017-05-23</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S33" s="3" t="n">
-        <v>191</v>
+        <v>3396</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>1</v>
@@ -3777,41 +3812,41 @@
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>zjp1997720/zhijian-ai-bluebook-workbuddy-harness</t>
+          <t>2FastLabs/agent-squad</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>204</v>
+        <v>7757</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>59.5</v>
+        <v>69.8</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>拆解 WorkBuddy 的提示词、记忆、插件等
-【原文】智见 AI 蓝皮书：拆解 WorkBuddy 的提示词、记忆、插件、专家、Skill 与安全边界。</t>
+          <t>管理多个AI代理和复杂对话的灵活框架
+【原文】Flexible and powerful framework for managing multiple AI agents and handling complex conversations</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -3821,7 +3856,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zjp1997720/zhijian-ai-bluebook-workbuddy-harness</t>
+          <t>https://github.com/2FastLabs/agent-squad</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -3830,14 +3865,18 @@
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>8.5</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3850,62 +3889,63 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, bluebook, harness, workbuddy, zhijian-ai</t>
+          <t>agentic-ai, agents, ai-agents, ai-agents-framework, anthropic, anthropic-claude, aws, aws-bedrock, aws-cdk, aws-lambda, chatbot, framework</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S34" s="3" t="n">
-        <v>24</v>
+        <v>778</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>vercel/satori</t>
+          <t>mex-memory/mex</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>13927</v>
+        <v>1572</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>57.8</v>
+        <v>64</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>将 HTML 和 CSS 转换为 SVG
-【原文】Enlightened library to convert HTML and CSS to SVG</t>
+          <t>为工程师和他们的AI代理提供团队记忆
+【原文】Team memory for engineers and their AI agents. Lives in your repo. Shared through Git.
+【依据】topics: knowledge-graph</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3920,7 +3960,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vercel/satori</t>
+          <t>https://github.com/mex-memory/mex</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3929,11 +3969,11 @@
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>8.26</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>MPL-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3953,21 +3993,21 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>css, image, image-generation, image-generator, jsx, opengraph-images, satori, svg, vercel</t>
+          <t>claude-code, claude-code-skills, cli-tool, code-graph, codex, context-management, cursor, developer-tools, documentation, knowledge-graph, llm, mcp-server</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>2022-01-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S35" s="3" t="n">
-        <v>1686</v>
+        <v>172</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>1</v>
@@ -3979,42 +4019,42 @@
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>digitalsamba/claude-code-video-toolkit</t>
+          <t>axoviq-ai/synthadoc</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2061</v>
+        <v>1175</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>52.6</v>
+        <v>54.5</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>AI原生视频生产工具包，支持Claude Code
-【原文】AI-native video production toolkit for Claude Code
-【依据】topics: ai-video-generator, claude-code, programmatic-video, text-to-speech, video-editing</t>
+          <t>将原始文档转换为结构化、本地优先的维基百科
+【原文】Synthadoc: An open-source LLM knowledge compilation engine that turns raw documents into structured, local-first wikis. A transparent, human-readable alternative to traditional RAG, which can be self-managed and self-improved without the use of any tools.
+【依据】topics: knowledge-graph</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -4024,7 +4064,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/digitalsamba/claude-code-video-toolkit</t>
+          <t>https://github.com/axoviq-ai/synthadoc</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4033,11 +4073,11 @@
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>7.52</v>
+        <v>7.78</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -4057,21 +4097,21 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>ai-video-generator, claude-code, developer-tools, elevenlabs, open-source, openclaw, playwright, programmatic-video, qwen-tts, remotion, text-to-speech, video-editing</t>
+          <t>agent-skills, agentic-ai, cli-tool, domain-adaptation, enterprise, enterprise-solutions, knowledge-graph, local-llm, obsidian-md, obsidian-plugin, personal-knowledge-management, pkm</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S36" s="3" t="n">
-        <v>274</v>
+        <v>151</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>1</v>
@@ -4083,31 +4123,32 @@
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-video-generator stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SandAI-org/MAGI-1</t>
+          <t>ModernRelay/omnigraph</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>3782</v>
+        <v>1102</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>52.3</v>
+        <v>50.8</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>实现大规模自回归视频生成
-【原文】MAGI-1: Autoregressive Video Generation at Scale</t>
+          <t>提供湖屋原生图引擎，支持git-style workflows
+【原文】Lakehouse native graph engine with git-style workflows
+【依据】topics: knowledge-graph, lakehouse</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -4127,7 +4168,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SandAI-org/MAGI-1</t>
+          <t>https://github.com/ModernRelay/omnigraph</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4136,16 +4177,16 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>7.47</v>
+        <v>7.25</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -4160,21 +4201,21 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>autoregressive, diffusion-models, video-generation</t>
+          <t>apache-arrow, context-graph, datafusion, graph-database, knowledge-graph, lakehouse, lance, mcp, rust, s3, versioning</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S37" s="3" t="n">
-        <v>506</v>
+        <v>152</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>1</v>
@@ -4186,42 +4227,42 @@
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Feelingeouncouple/Canva-Professional</t>
+          <t>videojs/video.js</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>598</v>
+        <v>39880</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>48.1</v>
+        <v>46.8</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Canva Pro云端工具包与自动化工作室
-【原文】Canva Pro Cloud Toolkit &amp; Automation Studio. Advanced graphic design assets, team collaboration workflows, premium template management, and visual content creation tools.
-【依据】topics: canva-app, canva-editor-tools, canva-export-tools, canva-free, canva-pro</t>
+          <t>提供HTML5视频播放功能
+【原文】Video.js - open source HTML5 video player
+【依据】topics: video-player</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -4231,7 +4272,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Feelingeouncouple/Canva-Professional</t>
+          <t>https://github.com/videojs/video.js</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4240,14 +4281,18 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>6.87</v>
+        <v>6.69</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4260,21 +4305,21 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>canva-app, canva-bulk-create, canva-editor-tools, canva-export-tools, canva-free, canva-full, canva-hack, canva-pro, canva-pro-team-2026, followers-ig, social-media-app, social-media-design</t>
+          <t>dash, hls, html, html5, html5-audio, html5-video, javascript, player, video, video-player, videojs</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2010-05-14</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>87</v>
+        <v>5962</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>1</v>
@@ -4286,26 +4331,27 @@
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>content automation in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>hao-ai-lab/FastVideo</t>
+          <t>jitsi/jitsi-meet</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>4363</v>
+        <v>29895</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>加速视频生成的统一推理和后训练框架
-【原文】A unified inference and post-training framework for accelerated video generation.</t>
+          <t>提供安全、简单且可扩展的视频会议服务
+【原文】Jitsi Meet - Secure, Simple and Scalable Video Conferences that you use as a standalone app or embed in your web application.
+【依据】topics: video-conferencing</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4315,7 +4361,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -4330,7 +4376,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hao-ai-lab/FastVideo</t>
+          <t>https://github.com/jitsi/jitsi-meet</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4339,7 +4385,7 @@
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>6.37</v>
+        <v>6.43</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
@@ -4348,7 +4394,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4363,21 +4409,21 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>diffusers, diffusion-models, distillation, inference, post-training, video-generation</t>
+          <t>debian, deep-video, jitsi, jitsi-meet, scalable-video-conferences, sfu, video, video-communication, video-conferencing, webrtc</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2013-12-16</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S39" s="3" t="n">
-        <v>685</v>
+        <v>4650</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>1</v>
@@ -4389,41 +4435,41 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>leejet/stable-diffusion.cpp</t>
+          <t>beclab/Olares</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>6948</v>
+        <v>5262</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>43.3</v>
+        <v>42.7</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>提供纯 C/C++ 的扩散模型推理
-【原文】Diffusion model(SD,Flux,Wan,Qwen Image,Z-Image,...) inference in pure C/C++</t>
+          <t>为始终在线代理的开源个人云操作系统
+【原文】Open-Source Personal Cloud OS for Always-On Agents</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -4433,7 +4479,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/leejet/stable-diffusion.cpp</t>
+          <t>https://github.com/beclab/Olares</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4442,16 +4488,16 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>6.19</v>
+        <v>6.1</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4466,21 +4512,21 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>ai, cplusplus, diffusion, flux, flux-dev, ggml, image-generation, image2image, img2img, latent-diffusion, ltx-video, qwen-image</t>
+          <t>agentic-ai, ai-agents, cloud-native, data-privacy, edge-ai, homelab, kubernetes, local-ai, model-serving, operating-system, personal-cloud, self-hosted</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S40" s="3" t="n">
-        <v>1123</v>
+        <v>863</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>1</v>
@@ -4492,26 +4538,27 @@
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>strawberrynine/ZiWeiDouShu-Master</t>
+          <t>huiliyi37/Tianshu-harness</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>47</v>
+        <v>522</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>41.2</v>
+        <v>39.7</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>提供紫微斗数大师级分析
-【原文】紫微斗数大师级分析，基于古籍 希夷先生《紫微斗数》，融合倪海厦《天纪》体系，含完整排盘算法、四化系统、格局知识库，可以算任意一年/月/日的感情/健康/财运/事业运/学业运/移民运。需要提供具体到小时的出生时间，和具体到市的出生地点。</t>
+          <t>终端编程智能体运行时，针对DeepSeek V4优化
+【原文】天枢 (Tianshu) 是一个基于harness工程的终端编程智能体运行时（Tui X Gui），针对DeepSeek V4 做了前缀缓存工程优化（长会话实测稳态命中率 97–99%）和深度适配。它跳出了传统 AI 编程助手把大模型仅当成“工具”的局限，基于认知虚拟机 (CVM)、自感知层和信息素（Stigmergy）自衰减记忆构建，让 AI 成为有独立判断与认知防护的“开发伙伴”。
+【依据】基于harness工程的终端编程智能体运行时，针对DeepSeek V4做了前缀缓存工程优化</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4526,7 +4573,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -4536,7 +4583,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/strawberrynine/ZiWeiDouShu-Master</t>
+          <t>https://github.com/huiliyi37/Tianshu-harness</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4545,14 +4592,18 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4563,19 +4614,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, coding-agent, context-management, deepseek, dsh, gui, harness, harness-engineering, prefix-cache, tui</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>1</v>
@@ -4587,41 +4642,42 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>古籍 in:name,description stars:&gt;20</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ModelEngine-Group/app-platform</t>
+          <t>FalkorDB/FalkorDB</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>1454</v>
+        <v>5983</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>19.3</v>
+        <v>36.5</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>提供大模型应用开发的集成声明式编程和低代码配置工具
-【原文】AppPlatform 是一个前沿的大模型应用工程，旨在通过集成的声明式编程和低代码配置工具，简化和优化大模型的训练与推理应用的开发过程。本工程为软件工程师和产品经理提供一个强大的、可扩展的环境，以支持从概念到部署的全流程 AI 应用开发。</t>
+          <t>提供高速图数据库，用于知识图谱
+【原文】A super fast Graph Database uses GraphBLAS under the hood for its sparse adjacency matrix graph representation. Our goal is to provide the best Knowledge Graph for LLM (GraphRAG).
+【依据】topics: knowledge-graph</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>视频产线/AI免费池</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考/可部署服务</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -4631,7 +4687,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ModelEngine-Group/app-platform</t>
+          <t>https://github.com/FalkorDB/FalkorDB</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -4640,16 +4696,16 @@
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>2.76</v>
+        <v>5.22</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4664,66 +4720,67 @@
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, agentic-workflow, ai, java, low-code</t>
+          <t>cloud-database, database, database-as-a-service, developer-tools, devtools, graph-database, graphrag, knowledge-graph, realtime-database</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S42" s="3" t="n">
-        <v>527</v>
+        <v>1147</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>the-wayee/OpenTV</t>
+          <t>LLMQuant/quant-mind</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>201</v>
+        <v>2825</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>18.1</v>
+        <v>36.3</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>短视频内容的策划与生产工具</t>
+          <t>量化金融领域的知识提取和检索框架
+【原文】QuantMind is an agent-native knowledge extraction and retrieval framework for quantitative finance.</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -4733,7 +4790,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/the-wayee/OpenTV</t>
+          <t>https://github.com/LLMQuant/quant-mind</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -4742,16 +4799,16 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>2.58</v>
+        <v>5.19</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -4764,56 +4821,60 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>agent, context-engineering, data, harness-engineering, knowledge, llm, pipeline, quantitative-finance, quantitative-research, workflow</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="S43" s="3" t="n">
-        <v>78</v>
+        <v>544</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>18534516725/llm-api-setup-guides</t>
+          <t>LadybugDB/ladybug</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>138</v>
+        <v>1724</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>16.9</v>
+        <v>35.8</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>中文AI API中转站与工具配置教程
-【原文】88篇中文 AI API中转站与工具配置教程：Codex API、Claude Code API、OpenAI-compatible API、Base URL、Cursor、Cherry Studio、计费验证与错误排查。
-【依据】topics: ai-api, api-proxy, api-relay, api-testing, cherry-studio, claude-api</t>
+          <t>提供图数据库服务
+【原文】LadybugDB a graph database
+【依据】topics: graph-database</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -4833,7 +4894,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/18534516725/llm-api-setup-guides</t>
+          <t>https://github.com/LadybugDB/ladybug</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -4842,7 +4903,7 @@
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>2.42</v>
+        <v>5.12</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
@@ -4851,7 +4912,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4866,68 +4927,67 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>ai-api, api-proxy, api-relay, api-testing, cherry-studio, chinese-tutorial, claude-api, claude-code, cline, codex-api, codex-cli, cursor</t>
+          <t>code-knowledge-base, code-knowledge-graph, cypher, cypher-query-language, database, graph, knowledge-graph</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S44" s="3" t="n">
-        <v>57</v>
+        <v>337</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>rfhdw0102/YouDaoNoteLM</t>
+          <t>urchade/GLiNER</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>201</v>
+        <v>3624</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>16.2</v>
+        <v>24.6</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>有道云笔记等内容的自动知识库沉淀与智能问答
-【原文】接入有道云笔记、本地文件、网页与音视频等内容，自动沉淀为可检索知识库；基于 RAG 精准引用你的资料，提供可靠的智能问答与内容生成。兼容主流大模型和向量模型，让知识真正为你所用。
-【依据】topics: YouDaoNoteLM, RAG, 智能问答</t>
+          <t>轻量级命名实体识别模型
+【原文】Generalist and Lightweight Model for Named Entity Recognition (Extract any entity types from texts)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -4937,7 +4997,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rfhdw0102/YouDaoNoteLM</t>
+          <t>https://github.com/urchade/GLiNER</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -4946,16 +5006,16 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>2.31</v>
+        <v>3.52</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -4968,65 +5028,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P45" s="6" t="inlineStr"/>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>information-extraction, large-language-models, named-entity-recognition, natural-language-processing, prompt-tuning</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S45" s="3" t="n">
-        <v>87</v>
+        <v>1030</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>RAG 知识库 in:name,description stars:&gt;200</t>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>FurkanGozukara/Stable-Diffusion</t>
+          <t>trustgraph-ai/trustgraph</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2765</v>
+        <v>2697</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>15.8</v>
+        <v>23.9</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 艺术生成和深度伪造工具。
-【原文】FLUX, Stable Diffusion, SDXL, SD3, LoRA, Fine Tuning, DreamBooth, Training, Automatic1111, Forge WebUI, SwarmUI, DeepFake, TTS, Animation, Text To Video, Tutorials, Guides, Lectures, Courses, ComfyUI, Google Colab, RunPod, Kaggle, NoteBooks, ControlNet, TTS, Voice Cloning, AI, AI News, ML, ML News, News, Tech, Tech News, Kohya, Midjourney, RunPod</t>
+          <t>基于超图的上下文编排层，构建统一语义上下文层
+【原文】The context orchestration layer powered by hypergraphs. Build a unified semantic context layer where agentic outcomes are deterministic and agent behavior is not just traceable, but cryptographically verifiable.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -5036,7 +5100,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FurkanGozukara/Stable-Diffusion</t>
+          <t>https://github.com/trustgraph-ai/trustgraph</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5045,16 +5109,16 @@
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>2.25</v>
+        <v>3.41</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -5069,24 +5133,24 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>ai-art, coding, deepfake-generation, dreambooth, education, flux-dev, flux-lora, generative-ai, guides, how-to, image-to-video-generation, kohya-webui</t>
+          <t>agent, agent-harness, context, context-engineering, context-graph, context-harness, context-orchestration, determinism, explainable-ai, graph, graph-engineering, help-wanted</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1227</v>
+        <v>791</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
@@ -5095,26 +5159,26 @@
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="47" ht="150" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>nndl/llm-beginner</t>
+          <t>BruceLanLan/augur</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>6730</v>
+        <v>526</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>13.7</v>
+        <v>23.7</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>提供大模型与智能体电子书和编程任务
-【原文】《大模型与智能体》电子书与 6 个编程任务：Transformer、mini-GPT、SFT/DPO、RAG、工具调用与编程智能体。</t>
+          <t>多智能体投资分析系统，提供投资大师分析及共识机制
+【原文】🦉 Augur — 多智能体投资分析系统。13位虚拟投资大师独立分析，加权共识机制，Bloomberg风格Web仪表盘。</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -5124,7 +5188,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -5139,7 +5203,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/nndl/llm-beginner</t>
+          <t>https://github.com/BruceLanLan/augur</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5148,7 +5212,7 @@
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>1.95</v>
+        <v>3.39</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -5172,24 +5236,24 @@
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>agent, fudannlp, llm, openmoss, step-by-step</t>
+          <t>ai-agents, investment-analysis, multi-agent, stock-analysis, value-investing</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>2017-03-29</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="S47" s="3" t="n">
-        <v>3451</v>
+        <v>155</v>
       </c>
       <c r="T47" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U47" s="3" t="inlineStr">
         <is>
@@ -5198,26 +5262,26 @@
       </c>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GalTransl/GalTransl</t>
+          <t>zjunlp/DeepKE</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2263</v>
+        <v>4478</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>支持大语言模型的 Galgame 自动化翻译解决方案
-【原文】支持GPT-4/Claude/Deepseek/Sakura等大语言模型的Galgame自动化翻译解决方案  Automated translation solution for visual novels supporting GPT-4/Claude/Deepseek/Sakura</t>
+          <t>知识图谱提取与构建工具
+【原文】[EMNLP 2022] An Open Toolkit for Knowledge Graph Extraction and Construction</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -5227,12 +5291,12 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -5242,7 +5306,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/GalTransl/GalTransl</t>
+          <t>https://github.com/zjunlp/DeepKE</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5251,11 +5315,11 @@
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>1.89</v>
+        <v>1.51</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -5275,52 +5339,52 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>ai, galgame, translater</t>
+          <t>attribute-extraction, chinese, deep-learning, deepke, document-level, few-shot, information-extraction, instructie, kg, knowledge-graph, knowprompt, lightner</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1197</v>
+        <v>2961</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Pangu-Immortal/hunter-ai-content-factory</t>
+          <t>socai-io/socai</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>391</v>
+        <v>184</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11.9</v>
+        <v>9.9</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>自动从多个平台采集热点，生成文章和插图。
-【原文】自动发布 24 小时情报系统：好文章的 80% 在于选题。Hunter AI 自动从 GitHub Trending、Twitter、HackerNews Reddit 等平台采集热点，用 AI 判断哪些值得写，自动生成文章和插图，自动发布。</t>
+          <t>为小红书优化的Web Use Agent
+【依据】topics: xhs, xiaohongshu</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -5330,7 +5394,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5345,7 +5409,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Pangu-Immortal/hunter-ai-content-factory</t>
+          <t>https://github.com/socai-io/socai</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5354,16 +5418,16 @@
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -5376,50 +5440,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P49" s="6" t="inlineStr"/>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>agent, browser-use, claude, codex, compute-use, linkedin, tiktok, xhs, xiaohongshu</t>
+        </is>
+      </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S49" s="3" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U49" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>sollyu/AndroidStudioChineseLanguagePack</t>
+          <t>LHRLAB/Graph-R1</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2494</v>
+        <v>591</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>10.7</v>
+        <v>7.6</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>提供 AndroidStudio 中文插件
-【原文】AndroidStudio中文插件(官方修改版本）</t>
+          <t>基于强化学习的GraphRAG框架研究资源
+【原文】[ICML 2026] Official resources of "Graph-R1: Towards Agentic GraphRAG Framework via End-to-end Reinforcement Learning".</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5429,7 +5497,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5444,7 +5512,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sollyu/AndroidStudioChineseLanguagePack</t>
+          <t>https://github.com/LHRLAB/Graph-R1</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5453,14 +5521,18 @@
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5473,57 +5545,57 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>android-studio, chinese, plugins</t>
+          <t>chain-of-thought, graphrag, hypergraph, reinforcement-learning</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="S50" s="3" t="n">
-        <v>1633</v>
+        <v>547</v>
       </c>
       <c r="T50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="51" ht="150" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>wfcz10086/AI-automatically-generates-novels</t>
+          <t>KRLabsOrg/LettuceDetect</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>936</v>
+        <v>605</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>10.2</v>
+        <v>7.3</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>基于 AI 和提示词的 AIGC 创作生产力工具
-【原文】一个基于ai +提示词 的aigc创作生产力工具， 已经有数百家工作室和个人作者通过该工具实现了快速、批量生成小说、剧本、镜头。</t>
+          <t>RAG输出验证工具，用于代码和工具的验证
+【原文】Span-level grounding verification for RAG, code, and tool-grounded AI outputs.</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -5543,7 +5615,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wfcz10086/AI-automatically-generates-novels</t>
+          <t>https://github.com/KRLabsOrg/LettuceDetect</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5552,11 +5624,11 @@
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -5574,50 +5646,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P51" s="6" t="inlineStr"/>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>bert, hallucination-detection, hallucination-evaluation, information-extraction, nlp, python, pytorch, token-classification</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S51" s="3" t="n">
-        <v>644</v>
+        <v>581</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U51" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>lornshrimp/Lorn.NovelWriteSkills</t>
+          <t>JabRef/jabref</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>205</v>
+        <v>4704</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>提供围绕小说创作工作流的AI写作资产库
-【原文】一个面向长篇网文 / 小说创作工作流的 AI 写作资产库。它不是“随手堆提示词”的仓库，而是一套围绕 题材设计 → 大纲搭建 → 章节创作 → 审阅润色 → 多平台改写 → 质量门禁 → 分发落盘 搭起来的可复用写作系统。</t>
+          <t>管理BibTeX和BibLaTeX (.bib)库的桌面应用程序
+【原文】Desktop app for managing BibTeX and BibLaTeX (.bib) libraries</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -5627,12 +5703,12 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -5642,7 +5718,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lornshrimp/Lorn.NovelWriteSkills</t>
+          <t>https://github.com/JabRef/jabref</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5651,16 +5727,16 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>PowerShell</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5675,52 +5751,52 @@
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai, novel, skills, writing-assistant</t>
+          <t>academia, academic-publications, ai, biblatex, bibliography, bibtex, citation, citation-generator, citation-style-language, citation-styles, hacktoberfest, jabref</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S52" s="3" t="n">
-        <v>148</v>
+        <v>4565</v>
       </c>
       <c r="T52" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>metasequoiaime/MSIME-Windows</t>
+          <t>alaskasquirrel/Email-newsletter-RSS</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>1335</v>
+        <v>1647</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>提供水杉输入法 Windows 产品
-【原文】水杉输入法 Windows 产品：TSF、Server、GUI、设置页与安装器。内测：tg: https://t.me/msimegroup QQ Group: 829919142</t>
+          <t>邮箱、新闻简报和RSS聚合工具
+【原文】邮箱 📧 newsletter RSS 荟萃 News</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -5730,12 +5806,12 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -5745,7 +5821,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/metasequoiaime/MSIME-Windows</t>
+          <t>https://github.com/alaskasquirrel/Email-newsletter-RSS</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5754,18 +5830,14 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>1.26</v>
+        <v>0.91</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>C++</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5778,21 +5850,21 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>chinese, ime, input-method, japanese, metasequoia, tsf, windows, windows-11</t>
+          <t>chinese, email, newsletter, rss</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S53" s="3" t="n">
-        <v>1061</v>
+        <v>1816</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>1</v>
@@ -5811,29 +5883,29 @@
     <row r="54" ht="150" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>renmengwen/MuseDock</t>
+          <t>monarch-initiative/ontogpt</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>110</v>
+        <v>1006</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>8.1</v>
+        <v>5.2</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>AI短视频创作与编辑工作台，整理来源，生成视频
-【原文】MuseDock 是一个本地优先的 AI 短视频创作与编辑工作台。输入一个选题，粘贴文章、GitHub 或抖音链接，也可以直接上传图片；MuseDock 会整理来源、补充研究、规划脚本与镜头，生成配音和 HTML 动画帧，最后在本机渲染成视频。</t>
+          <t>基于LLM的实体抽取工具，包括SPIRES
+【原文】LLM-based ontological extraction tools, including SPIRES</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -5848,7 +5920,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/renmengwen/MuseDock</t>
+          <t>https://github.com/monarch-initiative/ontogpt</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -5857,16 +5929,16 @@
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5879,50 +5951,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P54" s="6" t="inlineStr"/>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>ai, chat-gpt, data-modeling, gpt-3, information-extraction, language-models, large-language-models, linkml, llm, monarchinitiative, named-entity-recognition, ner</t>
+        </is>
+      </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S54" s="3" t="n">
-        <v>95</v>
+        <v>1345</v>
       </c>
       <c r="T54" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U54" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="55" ht="150" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Java-Edge/Java-Interview-Tutorial</t>
+          <t>LHRLAB/HyperGraphRAG</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2860</v>
+        <v>451</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Java/数据库/DDD/设计模式/微服务/中间件/AI大模型应用/区块链开发最佳实践教程
-【原文】请star，勿fork，因为爱force push！涵盖国际大厂Java/数据库/DDD/设计模式/微服务/中间件/AI大模型应用/区块链开发最佳实践。关注公众号【JavaEdge】，一起交流学习！</t>
+          <t>提供基于超图结构的检索增强生成资源
+【原文】[NeurIPS 2025] Official resources of "HyperGraphRAG: Retrieval-Augmented Generation via Hypergraph-Structured Knowledge Representation".</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -5932,7 +6008,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -5947,7 +6023,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Java-Edge/Java-Interview-Tutorial</t>
+          <t>https://github.com/LHRLAB/HyperGraphRAG</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -5956,16 +6032,16 @@
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>1.1</v>
+        <v>0.72</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -5980,52 +6056,52 @@
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>architecture, blockchain, ddd, java</t>
+          <t>graphrag, hypergraph, knowledge-graph, large-language-models</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="S55" s="3" t="n">
-        <v>2606</v>
+        <v>629</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V55" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="56" ht="150" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>go-ego/gse</t>
+          <t>dromara/dante-cloud</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2841</v>
+        <v>959</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>提供多语言 NLP 和文本分割工具
-【原文】Go efficient multilingual NLP and text segmentation; support English, Chinese, Japanese and others.</t>
+          <t>微服务云原生基座和AI Agent开发平台
+【原文】🐉 Dante Cloud 是支持阻塞式与响应式服务并行的微服务云原生基座和面向AI Agent开发的智能基座，基于领域驱动模型（DDD）设计，以高质量代码与低安全漏洞为核心，高度模块化、组件化，覆盖IoT设备认证、国家等保三级、接口国密数字信封加密等多层次安全体系，并提供多租户解决方案。独创“一套代码实现微服务和单体架构灵活切换”，赋能企业级智能应用构建。🔝🔝点个star 持续关注更新！</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -6035,7 +6111,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -6050,7 +6126,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/go-ego/gse</t>
+          <t>https://github.com/dromara/dante-cloud</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6059,7 +6135,7 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.84</v>
+        <v>0.49</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -6068,7 +6144,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -6083,12 +6159,12 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>chinese, english, go, gse, hmm, hmm-viterbi-algorithm, japanese, jieba, nlp, segment, trie</t>
+          <t>ai-agent, harness-engineering, iot, loki, microservices, monolith, monorepo, mqtt, nacos, rsocket, spring-ai, spring-ai-alibaba</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
@@ -6097,7 +6173,7 @@
         </is>
       </c>
       <c r="S56" s="3" t="n">
-        <v>3365</v>
+        <v>1939</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>1</v>
@@ -6109,26 +6185,26 @@
       </c>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="57" ht="150" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>AIPMAndy/FreeToken</t>
+          <t>ail-project/ail-framework</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>105</v>
+        <v>1013</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>收集免费 API Token 的获取方法和使用指南
-【原文】🎁 收集各种免费 API Token 的获取方法和使用指南</t>
+          <t>信息泄露分析框架
+【原文】AIL framework - Analysis Information Leak framework</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -6141,9 +6217,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -6153,7 +6229,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/AIPMAndy/FreeToken</t>
+          <t>https://github.com/ail-project/ail-framework</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6162,14 +6238,18 @@
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>0.82</v>
+        <v>0.43</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr"/>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6180,61 +6260,64 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P57" s="6" t="inlineStr"/>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>ail-framework, darkweb, darkweb-scraping, data-mining, information-extraction, information-security, leak</t>
+        </is>
+      </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2020-04-20</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S57" s="3" t="n">
-        <v>128</v>
+        <v>2333</v>
       </c>
       <c r="T57" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V57" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="58" ht="150" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>lihanghang/NLP-Knowledge-Graph</t>
+          <t>iMoonLab/HGNN</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>1766</v>
+        <v>849</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>自然语言处理、知识图谱、对话系统技术研究与应用
-【原文】自然语言处理、知识图谱、对话系统，大模型等技术研究与应用。
-【依据】topics: bert, deep-learning, knowledge-graph, llm, nlp</t>
+          <t>超图神经网络研究，基于PyTorch
+【原文】Hypergraph Neural Networks (AAAI 2019)</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>代码库/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6249,7 +6332,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lihanghang/NLP-Knowledge-Graph</t>
+          <t>https://github.com/iMoonLab/HGNN</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6258,7 +6341,7 @@
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
@@ -6282,67 +6365,67 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, bert, deep-learning, ernie, event-driven, kbqa, knowledge-graph, llm, machine-learning, ner, nlp</t>
+          <t>complex-data, deep-learning, hypergraph, hypergraph-neural-networks, pytorch</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>2019-01-29</t>
+          <t>2018-12-06</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="S58" s="3" t="n">
-        <v>2780</v>
+        <v>2834</v>
       </c>
       <c r="T58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U58" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>知识图谱 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="59" ht="150" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>neopen/story-shot-agent</t>
+          <t>pnnl/HyperNetX</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>183</v>
+        <v>711</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>自动解析剧本，生成视频提示词，支持角色和剧情一致性保持
-【原文】剧本分镜智能体（PenShot）：电影/动漫/短剧/小说→分镜→提示词→视频。| 基于LLM 通过 LangGraph+LlamaIndex实现任意格式剧本的自动解析，生成 Sora/Veo/Runway 等模型可用的连贯text-to-video提示词。保持角色/剧情跨片段一致，支持 MCP/REST API/Function Calls/A2A 多方式集成。（LLM-powered text-to-video-prompt agent. Break scripts into Sora/Veo-ready shots with character consistency）</t>
+          <t>超图分析可视化Python包
+【原文】Python package for hypergraph analysis and visualization.</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -6352,7 +6435,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/neopen/story-shot-agent</t>
+          <t>https://github.com/pnnl/HyperNetX</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6361,11 +6444,11 @@
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -6385,53 +6468,52 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>agent-to-agent, ai-filmmaking, ai-video-generation, character-consistency, function-calling, kling-ai, langgraph-agent, llm-agent, pika-labs, prompt-engineering, rag, screenplay</t>
+          <t>hypergraph, hypergraphs, knowledge-graph, property-hypergraphs, python, s-linegraph, simplicial-complexes, simplicial-homology</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="S59" s="3" t="n">
-        <v>321</v>
+        <v>2879</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V59" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="60" ht="150" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MoFox-Studio/Neo-MoFox</t>
+          <t>easy-graph/Easy-Graph</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>101</v>
+        <v>479</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 聊天机器人框架，旨在创造数字生命体。
-【原文】一个全新重构的 AI 聊天机器人框架，它的目标不仅仅是回答问题，而是创造一个真正的数字生命体。
-【依据】旨在创造一个真正的数字生命体。</t>
+          <t>提供高级网络分析方法，包括结构洞检测和网络嵌入等
+【原文】EasyGraph is an open-source network analysis library designed to cover advanced network processing methods. It includes functionalities for detecting structural hole spanners, network embedding, and various classic network analysis techniques.</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -6441,12 +6523,12 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -6456,7 +6538,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MoFox-Studio/Neo-MoFox</t>
+          <t>https://github.com/easy-graph/Easy-Graph</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -6465,11 +6547,11 @@
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -6489,52 +6571,52 @@
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, bot, chatbot</t>
+          <t>hypergraph, multiprocessing-optimization, network-analysis, python, structural-hole-theory</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S60" s="3" t="n">
-        <v>224</v>
+        <v>2271</v>
       </c>
       <c r="T60" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="61" ht="150" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>unraous/uxuescript</t>
+          <t>kahypar/kahypar</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>170</v>
+        <v>534</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>提供学习通自动刷课脚本。
-【原文】学习通一键全自动刷课脚本，支持后台刷课、倍速播放、自动回答互动题目，截止 2026/09/09 可用。（免安装打包版已发布至Release）</t>
+          <t>多级超图划分框架，提供高质量解决方案
+【原文】KaHyPar (Karlsruhe Hypergraph Partitioning) is a multilevel hypergraph partitioning framework providing direct k-way and recursive bisection based partitioning algorithms that compute solutions of very high quality.</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -6544,7 +6626,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -6559,7 +6641,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/unraous/uxuescript</t>
+          <t>https://github.com/kahypar/kahypar</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -6568,7 +6650,7 @@
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0.36</v>
+        <v>0.15</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
@@ -6577,7 +6659,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -6592,67 +6674,67 @@
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>chaoxing, education, javascript, xuexitong</t>
+          <t>algorithm-engineering, cpp, evolutionary-algorithms, graph, graph-algorithms, graph-partitioning, graphs, hypergraph, hypergraph-partitioning, hypergraphs, papers-with-code, partitioning</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2016-09-23</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="S61" s="3" t="n">
-        <v>469</v>
+        <v>3638</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="62" ht="150" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>mofahuizhang/Gn</t>
+          <t>yamafaktory/hypergraph</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>提供中医病机分析框架。
-【原文】Gn 通用病机分析框架——中医理论现代化、结构化与AI大模型结构复用</t>
+          <t>创建有向超图的数据结构库
+【原文】Hypergraph is a data structure library to create a directed hypergraph in which a hyperedge can join any number of vertices.</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>方剂知识线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -6662,7 +6744,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mofahuizhang/Gn</t>
+          <t>https://github.com/yamafaktory/hypergraph</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -6671,14 +6753,18 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6689,31 +6775,35 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P62" s="6" t="inlineStr"/>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>data, data-science, data-structure, data-structures, hypergraph, hypergraphs, rust, rust-lang, rustlang</t>
+        </is>
+      </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="S62" s="3" t="n">
-        <v>3</v>
+        <v>2163</v>
       </c>
       <c r="T62" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V62" s="6" t="inlineStr">
         <is>
-          <t>中医 大模型 in:name,description</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
